--- a/outputs/fl01_fl03_visual_runbook/KMS_FL01_FL03_Visual_Runbook_Tieng_Viet.xlsx
+++ b/outputs/fl01_fl03_visual_runbook/KMS_FL01_FL03_Visual_Runbook_Tieng_Viet.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cách dùng" sheetId="1" r:id="Rfab04330ce7f4ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_FL01" sheetId="2" r:id="R6db1fd5ffe41422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_FL02" sheetId="3" r:id="R36e1d6a3d4fc417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_FL03" sheetId="4" r:id="Rb0606330a39e48b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_E2E_Tổng hợp" sheetId="5" r:id="R1b6c357e57724d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dữ liệu mẫu" sheetId="6" r:id="R7c7e9ab784bf462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Checklist" sheetId="7" r:id="R210794f5ff264302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cách dùng" sheetId="1" r:id="R9581f5521a6d4814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_FL01" sheetId="2" r:id="Rffe9997442d74c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_FL02" sheetId="3" r:id="R9ff8c8da3fdc4a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_FL03" sheetId="4" r:id="R8fac217a578b4058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_E2E_Tổng hợp" sheetId="5" r:id="R4b665b47392c4b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dữ liệu mẫu" sheetId="6" r:id="R0ee131b43dc8468c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Checklist" sheetId="7" r:id="R80a7179512524539"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,6 +45,12 @@
       <x:b/>
       <x:sz val="10"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Inter"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF003366"/>
       <x:name val="Inter"/>
     </x:font>
   </x:fonts>
@@ -152,7 +158,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
@@ -259,8 +265,11 @@
     <x:xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -578,22 +587,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>KMS - Runbook trực quan FL-01 đến FL-03</x:v>
       </x:c>
     </x:row>
@@ -801,7 +810,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a3a658bfef4adb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a535df97b254806"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -819,22 +828,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>FL-01 - Tìm kiếm và sử dụng tri thức</x:v>
       </x:c>
     </x:row>
@@ -868,22 +877,22 @@
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node offline, SOP-NET-007.</x:v>
+        <x:v>Vai trò dùng trong luồng này: Kỹ thuật viên hiện trường - Minh Tran. Dữ liệu trọng tâm: CTN-1108, node mất kết nối, SOP-NET-007.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -945,10 +954,10 @@
         <x:v>Bấm tab Cơ sở tri thức ở thanh bên.</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>Từ khóa: node offline hoặc gateway.</x:v>
+        <x:v>Từ khóa: node mất kết nối hoặc cổng kết nối.</x:v>
       </x:c>
       <x:c r="E8" s="34" t="str">
-        <x:v>Màn hình tìm kiếm nâng cao hiển thị form lọc.</x:v>
+        <x:v>Màn hình tìm kiếm nâng cao hiển thị biểu mẫu lọc.</x:v>
       </x:c>
       <x:c r="F8" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=search</x:v>
@@ -962,16 +971,16 @@
         <x:v>Cơ sở tri thức</x:v>
       </x:c>
       <x:c r="C9" s="34" t="str">
-        <x:v>Nhập từ khóa và Asset ID rồi bấm Tìm kiếm.</x:v>
+        <x:v>Nhập từ khóa và mã tài sản rồi bấm Tìm kiếm.</x:v>
       </x:c>
       <x:c r="D9" s="34" t="str">
-        <x:v>Từ khóa: node offline gateway; Asset ID: CTN-1108.</x:v>
+        <x:v>Từ khóa: node mất kết nối cổng kết nối; mã tài sản: CTN-1108.</x:v>
       </x:c>
       <x:c r="E9" s="34" t="str">
         <x:v>Danh sách kết quả có SOP liên quan đến Smart Node mất kết nối.</x:v>
       </x:c>
       <x:c r="F9" s="35" t="str">
-        <x:v>http://127.0.0.1:5173/?screen=search-results&amp;query=node%20offline&amp;assetId=CTN-1108</x:v>
+        <x:v>http://127.0.0.1:5173/?screen=search-results&amp;query=node%20mất kết nối&amp;assetId=CTN-1108</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
@@ -982,7 +991,7 @@
         <x:v>Kết quả tìm kiếm</x:v>
       </x:c>
       <x:c r="C10" s="34" t="str">
-        <x:v>Bấm Mở nội dung ở card SOP-NET-007.</x:v>
+        <x:v>Bấm Mở nội dung ở thẻ SOP-NET-007.</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
         <x:v>SOP-NET-007.</x:v>
@@ -1002,10 +1011,10 @@
         <x:v>Chi tiết SOP</x:v>
       </x:c>
       <x:c r="C11" s="34" t="str">
-        <x:v>Đọc nhanh phần Applicability, Safety/PPE và Procedure Steps.</x:v>
+        <x:v>Đọc nhanh phần Applicability, Safety/phương tiện bảo hộ và Procedure Steps.</x:v>
       </x:c>
       <x:c r="D11" s="34" t="str">
-        <x:v>Chú ý các bước gateway, RF, reset cụm node.</x:v>
+        <x:v>Chú ý các bước cổng kết nối, RF, reset cụm node.</x:v>
       </x:c>
       <x:c r="E11" s="34" t="str">
         <x:v>Người xem hiểu SOP hiện tại chưa có bước kiểm tra nguồn dùng chung rõ ràng.</x:v>
@@ -1045,7 +1054,7 @@
         <x:v>Bấm Ghi nhận tri thức hiện trường nếu muốn đi tiếp sang FL-02.</x:v>
       </x:c>
       <x:c r="D13" s="34" t="str">
-        <x:v>Mã công việc: WO-2026-00421; Asset: CTN-1108.</x:v>
+        <x:v>Mã công việc: WO-2026-00421; Tài sản: CTN-1108.</x:v>
       </x:c>
       <x:c r="E13" s="34" t="str">
         <x:v>Prototype tạo draft submission hoặc mở tab gửi tri thức hiện trường.</x:v>
@@ -1082,7 +1091,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07feee0f793a4dfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4219e12843304ad4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1100,22 +1109,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>FL-02 - Gửi tri thức hiện trường và kiểm duyệt</x:v>
       </x:c>
     </x:row>
@@ -1209,7 +1218,7 @@
         <x:v>Mã công việc gần nhất: WO-2026-00421.</x:v>
       </x:c>
       <x:c r="E7" s="34" t="str">
-        <x:v>Thấy card công việc gần nhất và nút ghi nhận bài học.</x:v>
+        <x:v>Thấy thẻ công việc gần nhất và nút ghi nhận bài học.</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=request&amp;tab=field-capture</x:v>
@@ -1226,10 +1235,10 @@
         <x:v>Bấm Ghi nhận bài học từ công việc này.</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>Asset: CTN-1108; Loại lỗi: Mất kết nối; Severity: Cao.</x:v>
+        <x:v>Tài sản: CTN-1108; Loại lỗi: Mất kết nối; Severity: Cao.</x:v>
       </x:c>
       <x:c r="E8" s="34" t="str">
-        <x:v>Wizard mở bước Bối cảnh với dữ liệu được điền sẵn.</x:v>
+        <x:v>trình nhập liệu mở bước Bối cảnh với dữ liệu được điền sẵn.</x:v>
       </x:c>
       <x:c r="F8" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=field-submission&amp;id=SUB-2026-0042&amp;step=context</x:v>
@@ -1246,7 +1255,7 @@
         <x:v>Điền nguyên nhân, hành động sửa chữa và liên kết SOP đã dùng.</x:v>
       </x:c>
       <x:c r="D9" s="34" t="str">
-        <x:v>SOP đã dùng: SOP-NET-007 v2.1; bước liên quan: STEP-03, STEP-04; feedback: Incomplete.</x:v>
+        <x:v>SOP đã dùng: SOP-NET-007 v2.1; bước liên quan: STEP-03, STEP-04; phản hồi: Chưa đầy đủ.</x:v>
       </x:c>
       <x:c r="E9" s="34" t="str">
         <x:v>Form thể hiện SOP gap/deviation để làm căn cứ cập nhật SOP.</x:v>
@@ -1266,10 +1275,10 @@
         <x:v>Nhập bài học kinh nghiệm và đề xuất cập nhật SOP.</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
-        <x:v>Bài học: nhiều node cùng offline nên kiểm tra nguồn/tuyến cáp dùng chung trước khi thay node.</x:v>
+        <x:v>Bài học: nhiều node cùng mất kết nối nên kiểm tra nguồn/tuyến cáp dùng chung trước khi thay node.</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
-        <x:v>Đề xuất Update Existing, target SOP-NET-007, gap summary đủ rõ.</x:v>
+        <x:v>Đề xuất Cập nhật SOP hiện có, SOP mục tiêu SOP-NET-007, gap summary đủ rõ.</x:v>
       </x:c>
       <x:c r="F10" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=field-submission&amp;id=SUB-2026-0042&amp;step=evidence</x:v>
@@ -1363,7 +1372,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79a071e0c564be3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e2e5a8638fa4cc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1381,43 +1390,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>FL-03 - Tạo mới hoặc cập nhật SOP</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>Mục tiêu: Người biên soạn soạn Draft SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
+        <x:v>Mục tiêu: Người biên soạn soạn bản nháp SOP từ nhiệm vụ, Quản lý tri thức duyệt và xuất bản SOP phiên bản mới về FL-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1490,7 +1499,7 @@
         <x:v>Nhiệm vụ mẫu: SOPTASK-2026-008.</x:v>
       </x:c>
       <x:c r="E7" s="34" t="str">
-        <x:v>Thấy card Cập nhật SOP xử lý nhiều Smart Node mất kết nối.</x:v>
+        <x:v>Thấy thẻ Cập nhật SOP xử lý nhiều Smart Node mất kết nối.</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=sops&amp;tab=tasks</x:v>
@@ -1550,7 +1559,7 @@
         <x:v>Vai trò áp dụng: Kỹ thuật viên hiện trường, Người biên soạn.</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
-        <x:v>Người xem hiểu SOP dùng cho nhiều node offline trong cùng gateway/tuyến.</x:v>
+        <x:v>Người xem hiểu SOP dùng cho nhiều node mất kết nối trong cùng cổng kết nối/tuyến.</x:v>
       </x:c>
       <x:c r="F10" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=sop-editor&amp;id=SOPD-2026-0012&amp;step=scope</x:v>
@@ -1564,10 +1573,10 @@
         <x:v>Trình soạn - An toàn</x:v>
       </x:c>
       <x:c r="C11" s="34" t="str">
-        <x:v>Kiểm tra risk HIGH, PPE, mối nguy, biện pháp kiểm soát và điều kiện dừng.</x:v>
+        <x:v>Kiểm tra rủi ro CAO, phương tiện bảo hộ, mối nguy, biện pháp kiểm soát và điều kiện dừng.</x:v>
       </x:c>
       <x:c r="D11" s="34" t="str">
-        <x:v>PPE: găng tay cách điện, kính bảo hộ, áo phản quang.</x:v>
+        <x:v>phương tiện bảo hộ: găng tay cách điện, kính bảo hộ, áo phản quang.</x:v>
       </x:c>
       <x:c r="E11" s="34" t="str">
         <x:v>Có cảnh báo rủi ro cao và đầy đủ trường an toàn bắt buộc.</x:v>
@@ -1644,13 +1653,13 @@
         <x:v>Hàng đợi duyệt SOP</x:v>
       </x:c>
       <x:c r="C15" s="34" t="str">
-        <x:v>Đổi vai trò sang Quản lý tri thức và mở queue.</x:v>
+        <x:v>Đổi vai trò sang Quản lý tri thức và mở hàng đợi.</x:v>
       </x:c>
       <x:c r="D15" s="34" t="str">
         <x:v>Dùng nhanh: SOPD-2026-0015 vì đã ở trạng thái Đã gửi lại.</x:v>
       </x:c>
       <x:c r="E15" s="34" t="str">
-        <x:v>Hàng đợi có item để duyệt.</x:v>
+        <x:v>Hàng đợi có mục để duyệt.</x:v>
       </x:c>
       <x:c r="F15" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=sops&amp;tab=review</x:v>
@@ -1690,7 +1699,7 @@
         <x:v>Phiên bản: v3.0; Ngày hiệu lực: hôm nay; Ngày rà soát: +1 năm.</x:v>
       </x:c>
       <x:c r="E17" s="34" t="str">
-        <x:v>Điều hướng về SOP Detail và nhãn trạng thái hiển thị v3.0.</x:v>
+        <x:v>Điều hướng về Chi tiết SOP và nhãn trạng thái hiển thị v3.0.</x:v>
       </x:c>
       <x:c r="F17" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=sop-review-detail&amp;id=SOPD-2026-0015</x:v>
@@ -1710,7 +1719,7 @@
         <x:v>SOP-NET-007.</x:v>
       </x:c>
       <x:c r="E18" s="37" t="str">
-        <x:v>Timeline có v3.0 Đã xuất bản và v2.1 Bị thay thế.</x:v>
+        <x:v>Dòng thời gian có v3.0 Đã xuất bản và v2.1 Bị thay thế.</x:v>
       </x:c>
       <x:c r="F18" s="38" t="str">
         <x:v>http://127.0.0.1:5173/?screen=sop-version-history&amp;id=SOP-NET-007</x:v>
@@ -1724,7 +1733,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0126761a250a4d2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5c12e73db5748e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1742,22 +1751,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>Luồng demo tổng hợp từ FL-01 đến FL-03</x:v>
       </x:c>
     </x:row>
@@ -1865,16 +1874,16 @@
         <x:v>Cơ sở tri thức</x:v>
       </x:c>
       <x:c r="C8" s="34" t="str">
-        <x:v>Tìm SOP cho lỗi nhiều node offline.</x:v>
+        <x:v>Tìm SOP cho lỗi nhiều node mất kết nối.</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>Từ khóa: node offline gateway; Asset: CTN-1108.</x:v>
+        <x:v>Từ khóa: node mất kết nối cổng kết nối; Tài sản: CTN-1108.</x:v>
       </x:c>
       <x:c r="E8" s="34" t="str">
         <x:v>Có kết quả SOP-NET-007.</x:v>
       </x:c>
       <x:c r="F8" s="35" t="str">
-        <x:v>http://127.0.0.1:5173/?screen=search-results&amp;query=node%20offline&amp;assetId=CTN-1108</x:v>
+        <x:v>http://127.0.0.1:5173/?screen=search-results&amp;query=node%20mất kết nối&amp;assetId=CTN-1108</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -1911,7 +1920,7 @@
         <x:v>WO-2026-00421, CTN-1108.</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
-        <x:v>Wizard FL-02 mở với dữ liệu tình huống hiện trường.</x:v>
+        <x:v>trình nhập liệu FL-02 mở với dữ liệu tình huống hiện trường.</x:v>
       </x:c>
       <x:c r="F10" s="35" t="str">
         <x:v>http://127.0.0.1:5173/?screen=request&amp;tab=field-capture</x:v>
@@ -2065,7 +2074,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R450da9f182cd4d0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddfa655c002e4148"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2083,22 +2092,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>Dữ liệu mẫu cần nhớ khi demo</x:v>
       </x:c>
     </x:row>
@@ -2192,7 +2201,7 @@
         <x:v>Người tìm và sử dụng tri thức, gửi tình huống hiện trường.</x:v>
       </x:c>
       <x:c r="E7" s="34" t="str">
-        <x:v>Topbar vai trò switcher</x:v>
+        <x:v>Bộ chọn vai trò trên thanh trên</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
         <x:v>Không duyệt SOP</x:v>
@@ -2209,10 +2218,10 @@
         <x:v>FL-03</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>Người nhận nhiệm vụ và soạn Draft SOP.</x:v>
+        <x:v>Người nhận nhiệm vụ và soạn bản nháp SOP.</x:v>
       </x:c>
       <x:c r="E8" s="34" t="str">
-        <x:v>Topbar vai trò switcher</x:v>
+        <x:v>Bộ chọn vai trò trên thanh trên</x:v>
       </x:c>
       <x:c r="F8" s="35" t="str">
         <x:v>Không tự phê duyệt draft của mình</x:v>
@@ -2232,7 +2241,7 @@
         <x:v>Người kiểm duyệt, phê duyệt và xuất bản tri thức/SOP.</x:v>
       </x:c>
       <x:c r="E9" s="34" t="str">
-        <x:v>Topbar vai trò switcher</x:v>
+        <x:v>Bộ chọn vai trò trên thanh trên</x:v>
       </x:c>
       <x:c r="F9" s="35" t="str">
         <x:v>Dùng để xuất bản</x:v>
@@ -2249,13 +2258,13 @@
         <x:v>FL-01, FL-02</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
-        <x:v>Asset ID của CityTouch Node trong mã công việc.</x:v>
+        <x:v>mã tài sản của CityTouch Node trong mã công việc.</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
         <x:v>Tìm kiếm hoặc FL-02 Bối cảnh</x:v>
       </x:c>
       <x:c r="F10" s="35" t="str">
-        <x:v>Dùng với từ khóa node offline</x:v>
+        <x:v>Dùng với từ khóa node mất kết nối</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -2275,7 +2284,7 @@
         <x:v>Gửi yêu cầu &gt; Gửi tri thức hiện trường</x:v>
       </x:c>
       <x:c r="F11" s="35" t="str">
-        <x:v>Dữ liệu mẫu currentWorkOrder</x:v>
+        <x:v>Dữ liệu mẫu mã công việc hiện tại</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -2292,7 +2301,7 @@
         <x:v>SOP đang thiếu bước kiểm tra nguồn/tuyến cáp dùng chung.</x:v>
       </x:c>
       <x:c r="E12" s="34" t="str">
-        <x:v>SOP Detail</x:v>
+        <x:v>Chi tiết SOP</x:v>
       </x:c>
       <x:c r="F12" s="35" t="str">
         <x:v>Sau xuất bản thành v3.0</x:v>
@@ -2320,7 +2329,7 @@
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" s="33" t="str">
-        <x:v>Submission mẫu</x:v>
+        <x:v>Bản gửi mẫu</x:v>
       </x:c>
       <x:c r="B14" s="34" t="str">
         <x:v>SUB-2026-0043</x:v>
@@ -2329,13 +2338,13 @@
         <x:v>FL-02</x:v>
       </x:c>
       <x:c r="D14" s="34" t="str">
-        <x:v>Submission đã gửi, có đề xuất cập nhật SOP-NET-007.</x:v>
+        <x:v>Bản gửi đã gửi, có đề xuất cập nhật SOP-NET-007.</x:v>
       </x:c>
       <x:c r="E14" s="34" t="str">
         <x:v>Màn hình duyệt</x:v>
       </x:c>
       <x:c r="F14" s="35" t="str">
-        <x:v>Dùng để demo nhanh review/xuất bản</x:v>
+        <x:v>Dùng để demo nhanh duyệt/xuất bản</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="62" customHeight="1">
@@ -2446,7 +2455,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198e21eaf7ad48d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f53ac62b144774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2464,22 +2473,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>Checklist trước khi demo</x:v>
       </x:c>
     </x:row>
@@ -2604,7 +2613,7 @@
         <x:v>FL-01</x:v>
       </x:c>
       <x:c r="B9" s="34" t="str">
-        <x:v>Search ra SOP-NET-007.</x:v>
+        <x:v>Tìm kiếm ra SOP-NET-007.</x:v>
       </x:c>
       <x:c r="C9" s="34" t="str">
         <x:v>Kỹ thuật viên hiện trường</x:v>
@@ -2644,7 +2653,7 @@
         <x:v>FL-02</x:v>
       </x:c>
       <x:c r="B11" s="34" t="str">
-        <x:v>Submission có đề xuất cập nhật SOP.</x:v>
+        <x:v>Bản gửi có đề xuất cập nhật SOP.</x:v>
       </x:c>
       <x:c r="C11" s="34" t="str">
         <x:v>Quản lý tri thức</x:v>
@@ -2772,7 +2781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56055d9305804e8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ff3efbd3f0c46ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>